--- a/artfynd/A 10361-2026 artfynd.xlsx
+++ b/artfynd/A 10361-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96519962</v>
+        <v>96747124</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästbergen, Saxnäs, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512023.3483229128</v>
+        <v>512135</v>
       </c>
       <c r="R2" t="n">
-        <v>7207415.994449651</v>
+        <v>7207502</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96519961</v>
+        <v>96747561</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästbergen, Saxnäs, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511996.4111519314</v>
+        <v>511994</v>
       </c>
       <c r="R3" t="n">
-        <v>7207475.565160012</v>
+        <v>7207456</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,62 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96519959</v>
+        <v>97487064</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästbergen, Saxnäs, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512026.3112562044</v>
+        <v>512027</v>
       </c>
       <c r="R4" t="n">
-        <v>7207416.852917337</v>
+        <v>7207515</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96519960</v>
+        <v>97487065</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästbergen, Saxnäs, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512020.3495648004</v>
+        <v>512036</v>
       </c>
       <c r="R5" t="n">
-        <v>7207424.024307452</v>
+        <v>7207492</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,62 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96747896</v>
+        <v>97487067</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512115.4743616767</v>
+        <v>512043</v>
       </c>
       <c r="R6" t="n">
-        <v>7207479.009224509</v>
+        <v>7207488</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96747898</v>
+        <v>96747152</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511983.0278385101</v>
+        <v>512164</v>
       </c>
       <c r="R7" t="n">
-        <v>7207431.492785626</v>
+        <v>7207495</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96747813</v>
+        <v>96519959</v>
       </c>
       <c r="B8" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Hästbergen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512100.9207240773</v>
+        <v>512026</v>
       </c>
       <c r="R8" t="n">
-        <v>7207514.926344932</v>
+        <v>7207417</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,49 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96747388</v>
+        <v>96747735</v>
       </c>
       <c r="B9" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512111.9089972217</v>
+        <v>512095</v>
       </c>
       <c r="R9" t="n">
-        <v>7207522.166139921</v>
+        <v>7207612</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,19 +1422,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96747816</v>
+        <v>97487054</v>
       </c>
       <c r="B10" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512052.1557100638</v>
+        <v>512055</v>
       </c>
       <c r="R10" t="n">
-        <v>7207418.227025114</v>
+        <v>7207469</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1641,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96747812</v>
+        <v>96519961</v>
       </c>
       <c r="B11" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Hästbergen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512122.1116528926</v>
+        <v>511997</v>
       </c>
       <c r="R11" t="n">
-        <v>7207514.165908914</v>
+        <v>7207476</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,19 +1616,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96747814</v>
+        <v>96747464</v>
       </c>
       <c r="B12" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512112.7496187548</v>
+        <v>512142</v>
       </c>
       <c r="R12" t="n">
-        <v>7207523.862537251</v>
+        <v>7207490</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,19 +1713,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,22 +1735,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96747288</v>
+        <v>96747465</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512038.6124621557</v>
+        <v>512106</v>
       </c>
       <c r="R13" t="n">
-        <v>7207623.86988494</v>
+        <v>7207561</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1980,19 +1810,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +1832,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96747372</v>
+        <v>96747467</v>
       </c>
       <c r="B14" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512029.7737948628</v>
+        <v>511998</v>
       </c>
       <c r="R14" t="n">
-        <v>7207609.021081005</v>
+        <v>7207457</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,19 +1907,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,57 +1929,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96747389</v>
+        <v>97336408</v>
       </c>
       <c r="B15" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512114.7944320653</v>
+        <v>511959</v>
       </c>
       <c r="R15" t="n">
-        <v>7207542.070352547</v>
+        <v>7207252</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2201,22 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,27 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96747467</v>
+        <v>97487071</v>
       </c>
       <c r="B16" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,14 +2064,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511997.7590374586</v>
+        <v>512041</v>
       </c>
       <c r="R16" t="n">
-        <v>7207456.524164034</v>
+        <v>7207487</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2313,22 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96747464</v>
+        <v>97487027</v>
       </c>
       <c r="B17" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,34 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512142.1243931827</v>
+        <v>512055</v>
       </c>
       <c r="R17" t="n">
-        <v>7207490.545389211</v>
+        <v>7207469</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2425,22 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96747194</v>
+        <v>107608500</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,34 +2238,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärbergsviken, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512046.8160351056</v>
+        <v>511928</v>
       </c>
       <c r="R18" t="n">
-        <v>7207376.302362178</v>
+        <v>7207639</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2537,22 +2293,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,49 +2313,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96747213</v>
+        <v>96747369</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512105.3947140785</v>
+        <v>512158</v>
       </c>
       <c r="R19" t="n">
-        <v>7207561.078063066</v>
+        <v>7207492</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2652,19 +2393,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,16 +2425,11 @@
         <v>96747370</v>
       </c>
       <c r="B20" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2731,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512085.9007085347</v>
+        <v>512086</v>
       </c>
       <c r="R20" t="n">
-        <v>7207456.880046256</v>
+        <v>7207457</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2764,19 +2490,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,37 +2519,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96747963</v>
+        <v>96747371</v>
       </c>
       <c r="B21" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511994.7927310776</v>
+        <v>512116</v>
       </c>
       <c r="R21" t="n">
-        <v>7207456.512232536</v>
+        <v>7207565</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2876,19 +2587,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,37 +2616,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96747735</v>
+        <v>96747372</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512094.5951617693</v>
+        <v>512030</v>
       </c>
       <c r="R22" t="n">
-        <v>7207611.82266391</v>
+        <v>7207609</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2988,19 +2684,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,50 +2713,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96747817</v>
+        <v>97487075</v>
       </c>
       <c r="B23" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512004.4062843804</v>
+        <v>512055</v>
       </c>
       <c r="R23" t="n">
-        <v>7207489.564626761</v>
+        <v>7207469</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3097,22 +2778,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,50 +2810,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96747286</v>
+        <v>97487076</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512164.1422985194</v>
+        <v>511990</v>
       </c>
       <c r="R24" t="n">
-        <v>7207494.867613659</v>
+        <v>7207565</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3209,27 +2875,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Samlad</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,15 +2907,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96747195</v>
+        <v>96519960</v>
       </c>
       <c r="B25" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,34 +2918,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Hästbergen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512000.7049068792</v>
+        <v>512020</v>
       </c>
       <c r="R25" t="n">
-        <v>7207461.615072946</v>
+        <v>7207424</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3329,19 +2975,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,27 +2992,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96747815</v>
+        <v>96747194</v>
       </c>
       <c r="B26" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,21 +3015,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3408,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512116.4773790829</v>
+        <v>512047</v>
       </c>
       <c r="R26" t="n">
-        <v>7207545.039889913</v>
+        <v>7207376</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3441,19 +3072,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,15 +3101,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96747214</v>
+        <v>96747195</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,21 +3112,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3520,10 +3136,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512051.3081830597</v>
+        <v>512001</v>
       </c>
       <c r="R27" t="n">
-        <v>7207418.223600365</v>
+        <v>7207462</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3553,19 +3169,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,15 +3198,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96747369</v>
+        <v>97487085</v>
       </c>
       <c r="B28" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,34 +3209,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512158.2235652122</v>
+        <v>512035</v>
       </c>
       <c r="R28" t="n">
-        <v>7207491.457478041</v>
+        <v>7207492</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3662,22 +3263,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,37 +3295,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96747620</v>
+        <v>96747812</v>
       </c>
       <c r="B29" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512114.8752384057</v>
+        <v>512122</v>
       </c>
       <c r="R29" t="n">
-        <v>7207522.17818796</v>
+        <v>7207514</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3777,19 +3363,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,15 +3392,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96747465</v>
+        <v>96747813</v>
       </c>
       <c r="B30" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3832,21 +3403,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3856,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512105.3947140785</v>
+        <v>512101</v>
       </c>
       <c r="R30" t="n">
-        <v>7207561.078063066</v>
+        <v>7207515</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3889,19 +3460,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,15 +3489,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96747371</v>
+        <v>96747814</v>
       </c>
       <c r="B31" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3944,21 +3500,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512116.3965619199</v>
+        <v>512113</v>
       </c>
       <c r="R31" t="n">
-        <v>7207564.931902387</v>
+        <v>7207524</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4001,19 +3557,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,15 +3586,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96747287</v>
+        <v>96747815</v>
       </c>
       <c r="B32" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,21 +3597,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +3621,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512072.846448804</v>
+        <v>512117</v>
       </c>
       <c r="R32" t="n">
-        <v>7207436.510858337</v>
+        <v>7207545</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4113,19 +3654,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,15 +3683,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>96747867</v>
+        <v>96747816</v>
       </c>
       <c r="B33" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,21 +3694,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4192,10 +3718,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>512096.4600562523</v>
+        <v>512052</v>
       </c>
       <c r="R33" t="n">
-        <v>7207569.929845187</v>
+        <v>7207418</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4225,19 +3751,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,37 +3780,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96747870</v>
+        <v>96747817</v>
       </c>
       <c r="B34" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6486</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +3815,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>512108.3815369937</v>
+        <v>512004</v>
       </c>
       <c r="R34" t="n">
-        <v>7207556.011299036</v>
+        <v>7207489</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4337,19 +3848,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,15 +3877,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96747124</v>
+        <v>97487044</v>
       </c>
       <c r="B35" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,34 +3888,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>1467</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>512135.2961201296</v>
+        <v>511959</v>
       </c>
       <c r="R35" t="n">
-        <v>7207502.368586045</v>
+        <v>7207294</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4446,22 +3942,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,15 +3974,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96747152</v>
+        <v>97487045</v>
       </c>
       <c r="B36" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,34 +3985,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>512164.1422985194</v>
+        <v>511988</v>
       </c>
       <c r="R36" t="n">
-        <v>7207494.867613659</v>
+        <v>7207226</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4558,22 +4039,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,50 +4071,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96747871</v>
+        <v>97487046</v>
       </c>
       <c r="B37" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6486</v>
+        <v>1467</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hästbergen, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>512074.1297259816</v>
+        <v>512013</v>
       </c>
       <c r="R37" t="n">
-        <v>7207433.553245745</v>
+        <v>7207554</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4670,22 +4136,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,37 +4168,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96747561</v>
+        <v>96747867</v>
       </c>
       <c r="B38" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4752,10 +4203,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511993.5214569115</v>
+        <v>512096</v>
       </c>
       <c r="R38" t="n">
-        <v>7207456.507119942</v>
+        <v>7207570</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4785,19 +4236,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4827,12 +4268,7 @@
         <v>97336410</v>
       </c>
       <c r="B39" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4864,10 +4300,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511961.2864808515</v>
+        <v>511961</v>
       </c>
       <c r="R39" t="n">
-        <v>7207252.361765741</v>
+        <v>7207252</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4897,19 +4333,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4936,15 +4362,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>97336411</v>
+        <v>97487038</v>
       </c>
       <c r="B40" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4952,21 +4373,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4976,10 +4397,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511962.5663302173</v>
+        <v>511973</v>
       </c>
       <c r="R40" t="n">
-        <v>7207250.250478114</v>
+        <v>7207284</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5009,19 +4430,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5036,49 +4447,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97336409</v>
+        <v>97487039</v>
       </c>
       <c r="B41" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5088,10 +4494,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511955.3670349594</v>
+        <v>511974</v>
       </c>
       <c r="R41" t="n">
-        <v>7207248.951759608</v>
+        <v>7207242</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5121,19 +4527,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5148,27 +4544,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>97336408</v>
+        <v>97487040</v>
       </c>
       <c r="B42" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,21 +4567,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5200,10 +4591,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511959.1675455612</v>
+        <v>511956</v>
       </c>
       <c r="R42" t="n">
-        <v>7207252.35326898</v>
+        <v>7207296</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5233,19 +4624,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5260,49 +4641,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>97487065</v>
+        <v>98584382</v>
       </c>
       <c r="B43" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5312,10 +4688,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512036.1775371475</v>
+        <v>511568</v>
       </c>
       <c r="R43" t="n">
-        <v>7207492.232180693</v>
+        <v>7207765</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5342,22 +4718,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2022-01-29</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2022-01-29</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5372,62 +4748,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>97487082</v>
+        <v>96747620</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512043.4018475389</v>
+        <v>512115</v>
       </c>
       <c r="R44" t="n">
-        <v>7207487.18233988</v>
+        <v>7207522</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5454,22 +4825,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5489,57 +4850,52 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>97487067</v>
+        <v>96747963</v>
       </c>
       <c r="B45" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>498</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>512043.3984292579</v>
+        <v>511995</v>
       </c>
       <c r="R45" t="n">
-        <v>7207488.028827556</v>
+        <v>7207456</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5566,22 +4922,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5608,50 +4954,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>97487040</v>
+        <v>96519962</v>
       </c>
       <c r="B46" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511955.6024924548</v>
+        <v>512023</v>
       </c>
       <c r="R46" t="n">
-        <v>7207295.936904289</v>
+        <v>7207416</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5678,22 +5019,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5708,62 +5039,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>97487046</v>
+        <v>96747213</v>
       </c>
       <c r="B47" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>512013.4697110812</v>
+        <v>512106</v>
       </c>
       <c r="R47" t="n">
-        <v>7207553.934493523</v>
+        <v>7207561</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5790,22 +5116,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5832,50 +5148,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>97487045</v>
+        <v>96747214</v>
       </c>
       <c r="B48" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511987.6701543868</v>
+        <v>512051</v>
       </c>
       <c r="R48" t="n">
-        <v>7207225.377392216</v>
+        <v>7207418</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5902,22 +5213,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5944,37 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>97487085</v>
+        <v>97487082</v>
       </c>
       <c r="B49" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5984,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>512035.3300311772</v>
+        <v>512043</v>
       </c>
       <c r="R49" t="n">
-        <v>7207492.228760467</v>
+        <v>7207487</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6017,19 +5313,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6056,37 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>97487044</v>
+        <v>97487083</v>
       </c>
       <c r="B50" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6096,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511958.9995279259</v>
+        <v>512028</v>
       </c>
       <c r="R50" t="n">
-        <v>7207294.257411497</v>
+        <v>7207515</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6129,19 +5410,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6168,50 +5439,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>97487036</v>
+        <v>107608494</v>
       </c>
       <c r="B51" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Tvärbergsviken, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511973.025083286</v>
+        <v>511862</v>
       </c>
       <c r="R51" t="n">
-        <v>7207284.1549914</v>
+        <v>7207684</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6238,22 +5505,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6268,49 +5525,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>97487060</v>
+        <v>107897754</v>
       </c>
       <c r="B52" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6320,10 +5572,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511973.025083286</v>
+        <v>511958</v>
       </c>
       <c r="R52" t="n">
-        <v>7207284.1549914</v>
+        <v>7207680</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6350,22 +5602,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6385,57 +5637,52 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>97487061</v>
+        <v>96747388</v>
       </c>
       <c r="B53" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511954.7549307232</v>
+        <v>512112</v>
       </c>
       <c r="R53" t="n">
-        <v>7207295.933507008</v>
+        <v>7207522</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6462,22 +5709,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6497,57 +5734,52 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>97487075</v>
+        <v>96747389</v>
       </c>
       <c r="B54" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>6439</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>512054.4912935084</v>
+        <v>512115</v>
       </c>
       <c r="R54" t="n">
-        <v>7207469.450555049</v>
+        <v>7207542</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6574,22 +5806,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6609,22 +5831,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>97487027</v>
+        <v>97487018</v>
       </c>
       <c r="B55" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6632,21 +5849,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6656,10 +5873,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>512054.4912935084</v>
+        <v>511983</v>
       </c>
       <c r="R55" t="n">
-        <v>7207469.450555049</v>
+        <v>7207567</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6689,19 +5906,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6728,15 +5935,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>97487054</v>
+        <v>97336411</v>
       </c>
       <c r="B56" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6744,21 +5946,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6768,10 +5970,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>512054.4912935084</v>
+        <v>511962</v>
       </c>
       <c r="R56" t="n">
-        <v>7207469.450555049</v>
+        <v>7207250</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6801,19 +6003,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6828,27 +6020,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>97487071</v>
+        <v>97487060</v>
       </c>
       <c r="B57" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6856,21 +6043,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6880,10 +6067,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>512041.2830790197</v>
+        <v>511973</v>
       </c>
       <c r="R57" t="n">
-        <v>7207487.173784636</v>
+        <v>7207284</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6913,19 +6100,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6952,37 +6129,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>97487062</v>
+        <v>97487061</v>
       </c>
       <c r="B58" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6992,10 +6164,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>511987.1465342841</v>
+        <v>511955</v>
       </c>
       <c r="R58" t="n">
-        <v>7207566.52578476</v>
+        <v>7207296</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7025,19 +6197,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7064,37 +6226,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>97487038</v>
+        <v>97487055</v>
       </c>
       <c r="B59" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7104,10 +6261,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>511973.025083286</v>
+        <v>511988</v>
       </c>
       <c r="R59" t="n">
-        <v>7207284.1549914</v>
+        <v>7207569</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7137,19 +6294,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7176,50 +6323,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>97487039</v>
+        <v>96747896</v>
       </c>
       <c r="B60" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>511974.4680619878</v>
+        <v>512115</v>
       </c>
       <c r="R60" t="n">
-        <v>7207241.409253726</v>
+        <v>7207479</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7246,22 +6388,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7288,15 +6420,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>97487055</v>
+        <v>96747898</v>
       </c>
       <c r="B61" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7304,34 +6431,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>511988.405852123</v>
+        <v>511983</v>
       </c>
       <c r="R61" t="n">
-        <v>7207569.493521817</v>
+        <v>7207431</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7358,22 +6485,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7400,15 +6517,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>97487089</v>
+        <v>97336409</v>
       </c>
       <c r="B62" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7416,21 +6528,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7440,10 +6552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>511973.0284815417</v>
+        <v>511956</v>
       </c>
       <c r="R62" t="n">
-        <v>7207283.308446015</v>
+        <v>7207249</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7473,19 +6585,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7500,49 +6602,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>97487083</v>
+        <v>97487036</v>
       </c>
       <c r="B63" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7552,10 +6649,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>512028.0340541062</v>
+        <v>511973</v>
       </c>
       <c r="R63" t="n">
-        <v>7207515.054742942</v>
+        <v>7207284</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7585,19 +6682,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7624,37 +6711,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>97487066</v>
+        <v>97487089</v>
       </c>
       <c r="B64" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>498</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7664,10 +6746,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>512026.7628048819</v>
+        <v>511973</v>
       </c>
       <c r="R64" t="n">
-        <v>7207515.049616154</v>
+        <v>7207283</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7697,19 +6779,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7736,37 +6808,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>97487076</v>
+        <v>97487062</v>
       </c>
       <c r="B65" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7776,10 +6843,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>511990.5449819032</v>
+        <v>511987</v>
       </c>
       <c r="R65" t="n">
-        <v>7207564.423248382</v>
+        <v>7207566</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7809,19 +6876,9 @@
           <t>2021-11-21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7848,50 +6905,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>97487018</v>
+        <v>96747870</v>
       </c>
       <c r="B66" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>511983.3294512203</v>
+        <v>512109</v>
       </c>
       <c r="R66" t="n">
-        <v>7207567.356923454</v>
+        <v>7207556</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7918,22 +6970,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7960,55 +7002,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>97487035</v>
+        <v>96747871</v>
       </c>
       <c r="B67" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Hästbergen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>512044.2493549454</v>
+        <v>512074</v>
       </c>
       <c r="R67" t="n">
-        <v>7207487.185762399</v>
+        <v>7207434</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8035,22 +7067,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-11-21</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8077,15 +7099,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>98584382</v>
+        <v>97487035</v>
       </c>
       <c r="B68" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8093,34 +7110,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>511568.1361147879</v>
+        <v>512044</v>
       </c>
       <c r="R68" t="n">
-        <v>7207765.056468432</v>
+        <v>7207487</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8147,22 +7169,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8177,27 +7189,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>107627695</v>
+        <v>107608512</v>
       </c>
       <c r="B69" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8205,50 +7212,49 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tvärberget, Ås lm</t>
+          <t>Tvärbergsviken, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>511974.6897619674</v>
+        <v>511992</v>
       </c>
       <c r="R69" t="n">
-        <v>7207608.376156888</v>
+        <v>7207642</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8278,19 +7284,9 @@
           <t>2023-03-26</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>05:35</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>06:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8305,44 +7301,39 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anna-Sara Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>107627704</v>
+        <v>107897751</v>
       </c>
       <c r="B70" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8350,21 +7341,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8373,10 +7353,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>511974.6897619674</v>
+        <v>511951</v>
       </c>
       <c r="R70" t="n">
-        <v>7207608.376156888</v>
+        <v>7207760</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8403,22 +7383,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8445,15 +7425,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>107608500</v>
+        <v>107897753</v>
       </c>
       <c r="B71" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8461,35 +7436,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tvärbergsviken, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>511928.3806003935</v>
+        <v>511958</v>
       </c>
       <c r="R71" t="n">
-        <v>7207638.663227209</v>
+        <v>7207674</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8516,22 +7495,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8546,27 +7525,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>107608494</v>
+        <v>107627695</v>
       </c>
       <c r="B72" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8574,35 +7548,50 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tvärbergsviken, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>511861.6745258608</v>
+        <v>511975</v>
       </c>
       <c r="R72" t="n">
-        <v>7207683.682334875</v>
+        <v>7207608</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8634,7 +7623,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8644,7 +7633,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8659,27 +7648,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>107608512</v>
+        <v>107627703</v>
       </c>
       <c r="B73" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8687,16 +7671,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8704,32 +7688,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tvärbergsviken, Ås lm</t>
+          <t>Tvärberget, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>511991.5064801963</v>
+        <v>511975</v>
       </c>
       <c r="R73" t="n">
-        <v>7207641.455765331</v>
+        <v>7207608</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8761,7 +7746,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8771,7 +7756,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8786,27 +7771,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>107897753</v>
+        <v>107897755</v>
       </c>
       <c r="B74" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8814,16 +7794,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8831,10 +7811,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8843,10 +7827,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>511957.900997367</v>
+        <v>511979</v>
       </c>
       <c r="R74" t="n">
-        <v>7207673.909270874</v>
+        <v>7207595</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8878,7 +7862,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8888,7 +7872,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8915,32 +7899,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>107897751</v>
+        <v>107627704</v>
       </c>
       <c r="B75" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>103042</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8948,10 +7927,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8960,10 +7950,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>511950.7770648114</v>
+        <v>511975</v>
       </c>
       <c r="R75" t="n">
-        <v>7207759.794002185</v>
+        <v>7207608</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8990,22 +7980,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9029,118 +8019,6 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>107897754</v>
-      </c>
-      <c r="B76" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Tvärberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>511957.8772389624</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7207679.83430933</v>
-      </c>
-      <c r="S76" t="n">
-        <v>25</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2023-03-25</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
